--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -864,7 +864,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>189918.0</v>
+        <v>189937.0</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>16</v>
@@ -1154,7 +1154,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>435628.0</v>
+        <v>435772.0</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>16</v>
